--- a/daily_matches/job_matches_2026-04-17.xlsx
+++ b/daily_matches/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ronin Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, GCP Vertex AI, BigQuery</t>
+          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, CI/CD, Git, Snowflake, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c393b57d6602344</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Git, BigQuery, Kafka, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Azure ML, Data Lake, MLflow, Docker, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Dataflow, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, PySpark, Power BI, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, PySpark, Power BI, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Software Engineer III – Cloud Quality Engineering – Java / AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcc7311aad8bf06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Form Energy</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Git, Snowflake, Databricks, PySpark, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, FastAPI, CI/CD, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc93034e53f65ce</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3f783755a2f0d3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AIML Sr. Associate - DCL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Form Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Git, Snowflake, Databricks, PySpark, Python, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf29e34482062765</t>
+          <t>https://www.indeed.com/viewjob?jk=5423405c68c933e3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Fleet Management</t>
+          <t>Senior Software Engineer - Adobe Commerce</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, MySQL, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Docker, AKS, CI/CD, Git, MySQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fdcb5e870d3456</t>
+          <t>https://www.indeed.com/viewjob?jk=3792cfb2cda03a4b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Senior Engineer, Platform Engineering, AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Kubernetes, GitHub Actions, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=63d3fb797602d95b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full-Stack (API/Software Development/Microservices)</t>
+          <t>Data Science Senior Associate - Card Data Analytics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2ca1c1eff8c97e</t>
+          <t>https://www.indeed.com/viewjob?jk=5622cf9905f4db61</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full-Stack (API/Software Development/Microservices)</t>
+          <t>Sr. AI / Embedded ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>E-Space</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Saratoga, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Cortex, TensorFlow, PyTorch, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,77 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b349d7e67dee57d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Full-Stack (API/Software Development/Microservices)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0b551f679c7a68</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Gen Digital Inc.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=739259f946595822</t>
+          <t>https://www.indeed.com/viewjob?jk=80fd9183764f3538</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-17.xlsx
+++ b/daily_matches/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Enterprise Cybersecurity Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, CI/CD, Git, Snowflake, PySpark</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Tableau, Power BI, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5c935b32c7ce15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Azure ML, Data Lake, MLflow, Docker, AKS, CI/CD</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=61c9645fcdf8d390</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, PySpark, Power BI, Matplotlib, Seaborn, Python</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a5ebdf2f0ec8f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, PySpark, Power BI, Matplotlib, Seaborn, Python</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=a2548ff027a81733</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, MySQL, NoSQL, Python, SQL</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7392f3cd1cd74e9a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Quality Engineering – Java / AWS</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcc7311aad8bf06</t>
+          <t>https://www.indeed.com/viewjob?jk=25179c617991dbcd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, FastAPI, CI/CD, R</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3f783755a2f0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=130195ef368d1229</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AIML Sr. Associate - DCL</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423405c68c933e3</t>
+          <t>https://www.indeed.com/viewjob?jk=54fcabc84a90db57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Adobe Commerce</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, AKS, CI/CD, Git, MySQL, SQL, R, Optimization</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3792cfb2cda03a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c114d76aa4b24e64</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, Platform Engineering, AI</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Kubernetes, GitHub Actions, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d3fb797602d95b</t>
+          <t>https://www.indeed.com/viewjob?jk=59c6380629340cd8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate - Card Data Analytics</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622cf9905f4db61</t>
+          <t>https://www.indeed.com/viewjob?jk=e1758bd8035a2b67</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. AI / Embedded ML Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>E-Space</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saratoga, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Cortex, TensorFlow, PyTorch, Python, R, Optimization</t>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,392 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80fd9183764f3538</t>
+          <t>https://www.indeed.com/viewjob?jk=17736e9e8558c607</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dca4ecbf7cbe0e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=256d33a5d00d52e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8219098cfc006d4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0128e468ee5d06c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6927b6904048dc5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55c6599af17ff8a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9742a9041a5dfa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=020d180f72161f5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bdccba70743b503</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d9f5e68e43cfeb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Consultant, Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dell Technologies</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0752c814a66bf53</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-17.xlsx
+++ b/daily_matches/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enterprise Cybersecurity Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Tableau, Power BI, Seaborn, Python, SQL</t>
+          <t>Generative AI, RAG, BigQuery, Data Lake, Dataflow, Snowflake, Databricks, BigQuery, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5c935b32c7ce15</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Senior Back End JS Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c9645fcdf8d390</t>
+          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>AI/ML Engineer - Local to Dallas - Face to Face Interview in Dallas,TX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, Hugging Face, Pinecone, Prompt Engineering, S3, EC2, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a5ebdf2f0ec8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a7f31721ffc30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data and AI Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2548ff027a81733</t>
+          <t>https://www.indeed.com/viewjob?jk=a9087c01d26abe93</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Innovation Software Engineer L3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7392f3cd1cd74e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c6238e4345d574</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Artificial Intelligence (AI) Developer – Dynamics Contact Center Solutions</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25179c617991dbcd</t>
+          <t>https://www.indeed.com/viewjob?jk=ea1438a3749cfbee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data Scientist, Generative &amp; Agentic AI Solutions: Senior Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130195ef368d1229</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d5668f5e68d199</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data Scientist, Generative &amp; Agentic AI Solutions</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fcabc84a90db57</t>
+          <t>https://www.indeed.com/viewjob?jk=9aacbffbde2a611b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,507 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, AKS, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114d76aa4b24e64</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59c6380629340cd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1758bd8035a2b67</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17736e9e8558c607</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7dca4ecbf7cbe0e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=256d33a5d00d52e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8219098cfc006d4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0128e468ee5d06c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6927b6904048dc5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55c6599af17ff8a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9742a9041a5dfa5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=020d180f72161f5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bdccba70743b503</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>YO IT CONSULTING</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d9f5e68e43cfeb6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Consultant, Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dell Technologies</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Round Rock, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0752c814a66bf53</t>
+          <t>https://www.indeed.com/viewjob?jk=132f905b876b6514</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-17.xlsx
+++ b/daily_matches/job_matches_2026-04-17.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Data Lake, Dataflow, Snowflake, Databricks, BigQuery, Kafka, PostgreSQL</t>
+          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Back End JS Developer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL</t>
+          <t>RAG, Synapse, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a9e3b0a9c943d41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Local to Dallas - Face to Face Interview in Dallas,TX</t>
+          <t>Senior Forward-Deployed Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Hugging Face, Pinecone, Prompt Engineering, S3, EC2, FastAPI, Docker</t>
+          <t>S3, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a7f31721ffc30</t>
+          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data and AI Scientist</t>
+          <t>Cloud Application Development Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Databricks, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9087c01d26abe93</t>
+          <t>https://www.indeed.com/viewjob?jk=34d4cf06a4d58d99</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Innovation Software Engineer L3</t>
+          <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>S3, EC2, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c6238e4345d574</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb676fb8407e921</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Developer – Dynamics Contact Center Solutions</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, Kafka, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, CI/CD, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea1438a3749cfbee</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative &amp; Agentic AI Solutions: Senior Consultant</t>
+          <t>Senior Software Engineer – Backend New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+          <t>S3, EC2, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d5668f5e68d199</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative &amp; Agentic AI Solutions</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Glue, Hadoop, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aacbffbde2a611b</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Sr Analyst - Scheduling Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Frontier Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, AKS, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132f905b876b6514</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4f00929ccd08ed</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-17.xlsx
+++ b/daily_matches/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>BigQuery, Data Lake, Kinesis, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=b61d40c84be0641c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>REDICA Systems</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, LLaMA, Mistral, Pinecone, AWS SageMaker, FastAPI, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a9e3b0a9c943d41</t>
+          <t>https://www.indeed.com/viewjob?jk=9221ae855692024c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Forward-Deployed Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Quicksight</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
+          <t>https://www.indeed.com/viewjob?jk=c174e4a43011a2c9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Application Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Ritchie Bros.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Databricks, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d4cf06a4d58d99</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0bf0ea1a15ff6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>k1x</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb676fb8407e921</t>
+          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, CI/CD, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Hadoop, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e054d834b805e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend New</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Software Engineer-Java and Angular</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Glue, Hadoop, NoSQL, Python, SQL, R, Scala</t>
+          <t>Git, PostgreSQL, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d2832de4a4a8f6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Analyst - Scheduling Analytics</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frontier Airlines</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,252 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4f00929ccd08ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a479bbf0fe314c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Westerville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=824e17ddc3b88405</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Westerville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19801f701a559221</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Westerville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be6c05426518ffbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Westerville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fcfef6f074293d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Westerville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e762701c1516f27a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DATA ANALYST L3(CONTRACT)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b2876e8b1e32d13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CRUNCHTIME</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=786e3ed6998e528a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-17.xlsx
+++ b/daily_matches/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, Kinesis, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61d40c84be0641c</t>
+          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REDICA Systems</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, LLaMA, Mistral, Pinecone, AWS SageMaker, FastAPI, Snowflake, NoSQL</t>
+          <t>Generative AI, RAG, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9221ae855692024c</t>
+          <t>https://www.indeed.com/viewjob?jk=c76e322a4d3ade18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Quicksight</t>
+          <t>Generative AI, RAG, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c174e4a43011a2c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e762c929a195ba8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ritchie Bros.</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>RAG, Gemini, Copilot, S3, EC2, Redshift, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0bf0ea1a15ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>k1x</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
+          <t>RAG, Gemini, Copilot, S3, EC2, Redshift, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Hadoop, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e054d834b805e</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, Gemini, Prompt Engineering, Azure ML, Data Lake, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer-Java and Angular</t>
+          <t>Data Science, Machine Learning &amp; AI Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>FullSteam LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Git, PostgreSQL, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Glue, Athena, Git, MySQL, Matplotlib</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d2832de4a4a8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b64bf62bfb941f3e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Ritchie Bros.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a479bbf0fe314c</t>
+          <t>https://www.indeed.com/viewjob?jk=7478f0c13777c0ac</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Redshift, BigQuery, CI/CD, Git, Databricks, BigQuery, Redshift, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e17ddc3b88405</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Senior Software Engineer, Global Banking &amp; Markets, Equities Trading Technology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19801f701a559221</t>
+          <t>https://www.indeed.com/viewjob?jk=bae3cd3ab58e9679</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Associate Systems Integration &amp; Data Automati</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Media Source</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Terraform, Git, PostgreSQL, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6c05426518ffbf</t>
+          <t>https://www.indeed.com/viewjob?jk=c12b814500e81cdc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fcfef6f074293d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d9aa6cd6a22aa23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Snowflake, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e762701c1516f27a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d78e5b383f60bee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DATA ANALYST L3(CONTRACT)</t>
+          <t>Forward Deployed AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,672 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2876e8b1e32d13</t>
+          <t>https://www.indeed.com/viewjob?jk=9c59fc47260e9e5d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CRUNCHTIME</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KNOTCH, INC.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80fc137ae078a0c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Developer Experience (DevEx) Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Veracross</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Wakefield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ab10c88277bdef0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Full-stack)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UMB Financial Corporation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist (Supply Chain)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc42db74561e942b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineering - SRE Data - Software Engineer - Associate - Dallas</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0168418d41e2051</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Python</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Data Recognition Corporation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Maple Grove, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=786e3ed6998e528a</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1415cb981784330</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Entry Level &amp; Senior Software Engineer, AI Software Platform (Onsite)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6cb18bcd77e6c91</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer, EB Applied AI and Analytics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3722c3a94eb2584c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer, EB Applied AI and Analytics</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55e09a61e3de38fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer, EB Applied AI and Analytics</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffe685f96d382ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Handshake</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcbe27e7fe6a96fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Handshake</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2f97a457d802bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer III/Senior (AI and Gen AI)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Expeditors</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Terraform, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc8e652f785dac8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Engineer III/Senior (AI and Gen AI)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Expeditors</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Terraform, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae6ac9cee73c897b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Engineer III/Senior (AI and Gen AI)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Expeditors</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ellenwood, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Terraform, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e41a42297fee1db</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Engineer III/Senior (AI and Gen AI)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Expeditors</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Romulus, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Terraform, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a9d2bbb0436fa34</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TargetPath Solutions</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Data Analyst</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9662db59595d61c9</t>
         </is>
       </c>
     </row>
